--- a/data/ground_truth/GTRA.xlsx
+++ b/data/ground_truth/GTRA.xlsx
@@ -98,7 +98,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -131,6 +131,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="41" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -410,7 +411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA40"/>
+  <dimension ref="A1:AA49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="59.6640625" customWidth="1" min="1" max="1"/>
@@ -643,47 +644,51 @@
       <c r="C4" s="18" t="n">
         <v>1414582709919</v>
       </c>
-      <c r="D4" s="18" t="n">
+      <c r="D4" s="20" t="n">
+        <v>1740079004309</v>
+      </c>
+      <c r="E4" s="20" t="n">
+        <v>1414582709919</v>
+      </c>
+      <c r="F4" s="20" t="n">
         <v>1242804936571</v>
       </c>
-      <c r="E4" s="18" t="n">
+      <c r="G4" s="20" t="n">
         <v>1092421914566</v>
       </c>
-      <c r="F4" s="18" t="n">
+      <c r="H4" s="20" t="n">
         <v>1021734463181</v>
       </c>
-      <c r="G4" s="18" t="n">
+      <c r="I4" s="20" t="n">
         <v>1020153134914</v>
       </c>
-      <c r="H4" s="18" t="n">
+      <c r="J4" s="20" t="n">
         <v>989890084157</v>
       </c>
-      <c r="I4" s="18" t="n">
+      <c r="K4" s="20" t="n">
         <v>969955345450</v>
       </c>
-      <c r="J4" s="18" t="n">
+      <c r="L4" s="20" t="n">
         <v>973186701838</v>
       </c>
-      <c r="K4" s="18" t="n">
+      <c r="M4" s="20" t="n">
         <v>1009256528341</v>
       </c>
-      <c r="L4" s="18" t="n">
+      <c r="N4" s="20" t="n">
         <v>941311157349</v>
       </c>
-      <c r="M4" s="18" t="n">
+      <c r="O4" s="20" t="n">
         <v>921720459761</v>
       </c>
-      <c r="N4" s="18" t="n">
+      <c r="P4" s="20" t="n">
         <v>813614754558</v>
       </c>
-      <c r="O4" s="18" t="n">
+      <c r="Q4" s="20" t="n">
         <v>737307899123</v>
       </c>
-      <c r="P4" s="18" t="n">
+      <c r="R4" s="20" t="n">
         <v>684826152989</v>
       </c>
-      <c r="Q4" s="18" t="n"/>
-      <c r="R4" s="18" t="n"/>
       <c r="S4" s="18" t="n"/>
       <c r="T4" s="5" t="n"/>
       <c r="U4" s="7" t="n"/>
@@ -706,47 +711,51 @@
       <c r="C5" s="18" t="n">
         <v>279945979244</v>
       </c>
-      <c r="D5" s="18" t="n">
+      <c r="D5" s="20" t="n">
+        <v>357569040589</v>
+      </c>
+      <c r="E5" s="20" t="n">
+        <v>279945979244</v>
+      </c>
+      <c r="F5" s="20" t="n">
         <v>285904361224</v>
       </c>
-      <c r="E5" s="18" t="n">
+      <c r="G5" s="20" t="n">
         <v>256084951495</v>
       </c>
-      <c r="F5" s="18" t="n">
+      <c r="H5" s="20" t="n">
         <v>240605013483</v>
       </c>
-      <c r="G5" s="18" t="n">
+      <c r="I5" s="20" t="n">
         <v>224998895107</v>
       </c>
-      <c r="H5" s="18" t="n">
+      <c r="J5" s="20" t="n">
         <v>193749178955</v>
       </c>
-      <c r="I5" s="18" t="n">
+      <c r="K5" s="20" t="n">
         <v>161089530656</v>
       </c>
-      <c r="J5" s="18" t="n">
+      <c r="L5" s="20" t="n">
         <v>149381817741</v>
       </c>
-      <c r="K5" s="18" t="n">
+      <c r="M5" s="20" t="n">
         <v>178242590275</v>
       </c>
-      <c r="L5" s="18" t="n">
+      <c r="N5" s="20" t="n">
         <v>121176804224</v>
       </c>
-      <c r="M5" s="18" t="n">
+      <c r="O5" s="20" t="n">
         <v>110953728308</v>
       </c>
-      <c r="N5" s="18" t="n">
+      <c r="P5" s="20" t="n">
         <v>102188935358</v>
       </c>
-      <c r="O5" s="18" t="n">
+      <c r="Q5" s="20" t="n">
         <v>97760865990</v>
       </c>
-      <c r="P5" s="18" t="n">
+      <c r="R5" s="20" t="n">
         <v>73761021797</v>
       </c>
-      <c r="Q5" s="18" t="n"/>
-      <c r="R5" s="18" t="n"/>
       <c r="S5" s="18" t="n"/>
       <c r="T5" s="5" t="n"/>
       <c r="U5" s="7" t="n"/>
@@ -769,47 +778,51 @@
       <c r="C6" s="18" t="n">
         <v>20409301364</v>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="20" t="n">
+        <v>29716666451</v>
+      </c>
+      <c r="E6" s="20" t="n">
+        <v>20409301364</v>
+      </c>
+      <c r="F6" s="20" t="n">
         <v>19695706377</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="G6" s="20" t="n">
         <v>14653796710</v>
       </c>
-      <c r="F6" s="18" t="n">
+      <c r="H6" s="20" t="n">
         <v>14112835723</v>
       </c>
-      <c r="G6" s="18" t="n">
+      <c r="I6" s="20" t="n">
         <v>13769104184</v>
       </c>
-      <c r="H6" s="18" t="n">
+      <c r="J6" s="20" t="n">
         <v>8528119944</v>
       </c>
-      <c r="I6" s="18" t="n">
+      <c r="K6" s="20" t="n">
         <v>9393862468</v>
       </c>
-      <c r="J6" s="18" t="n">
+      <c r="L6" s="20" t="n">
         <v>8765089846</v>
       </c>
-      <c r="K6" s="18" t="n">
+      <c r="M6" s="20" t="n">
         <v>60303440517</v>
       </c>
-      <c r="L6" s="18" t="n">
+      <c r="N6" s="20" t="n">
         <v>16057258132</v>
       </c>
-      <c r="M6" s="18" t="n">
+      <c r="O6" s="20" t="n">
         <v>12850012053</v>
       </c>
-      <c r="N6" s="18" t="n">
+      <c r="P6" s="20" t="n">
         <v>11051322582</v>
       </c>
-      <c r="O6" s="18" t="n">
+      <c r="Q6" s="20" t="n">
         <v>25751037598</v>
       </c>
-      <c r="P6" s="18" t="n">
+      <c r="R6" s="20" t="n">
         <v>8759584740</v>
       </c>
-      <c r="Q6" s="18" t="n"/>
-      <c r="R6" s="18" t="n"/>
       <c r="S6" s="18" t="n"/>
       <c r="T6" s="5" t="n"/>
       <c r="U6" s="7" t="n"/>
@@ -832,47 +845,51 @@
       <c r="C7" s="18" t="n">
         <v>1007851247418</v>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="20" t="n">
+        <v>1298825565646</v>
+      </c>
+      <c r="E7" s="20" t="n">
+        <v>1007851247418</v>
+      </c>
+      <c r="F7" s="20" t="n">
         <v>856251177156</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="G7" s="20" t="n">
         <v>730612108307</v>
       </c>
-      <c r="F7" s="18" t="n">
+      <c r="H7" s="20" t="n">
         <v>672036868836</v>
       </c>
-      <c r="G7" s="18" t="n">
+      <c r="I7" s="20" t="n">
         <v>681840780948</v>
       </c>
-      <c r="H7" s="18" t="n">
+      <c r="J7" s="20" t="n">
         <v>669483382092</v>
       </c>
-      <c r="I7" s="18" t="n">
+      <c r="K7" s="20" t="n">
         <v>659794391223</v>
       </c>
-      <c r="J7" s="18" t="n">
+      <c r="L7" s="20" t="n">
         <v>671856600123</v>
       </c>
-      <c r="K7" s="18" t="n">
+      <c r="M7" s="20" t="n">
         <v>717062907204</v>
       </c>
-      <c r="L7" s="18" t="n">
+      <c r="N7" s="20" t="n">
         <v>659149682105</v>
       </c>
-      <c r="M7" s="18" t="n">
+      <c r="O7" s="20" t="n">
         <v>655152105799</v>
       </c>
-      <c r="N7" s="18" t="n">
+      <c r="P7" s="20" t="n">
         <v>553362078527</v>
       </c>
-      <c r="O7" s="18" t="n">
+      <c r="Q7" s="20" t="n">
         <v>482217445372</v>
       </c>
-      <c r="P7" s="18" t="n">
+      <c r="R7" s="20" t="n">
         <v>488840075078</v>
       </c>
-      <c r="Q7" s="18" t="n"/>
-      <c r="R7" s="18" t="n"/>
       <c r="S7" s="18" t="n"/>
       <c r="T7" s="5" t="n"/>
       <c r="U7" s="7" t="n"/>
@@ -895,47 +912,51 @@
       <c r="C8" s="18" t="n">
         <v>45503369944</v>
       </c>
-      <c r="D8" s="18" t="n">
+      <c r="D8" s="20" t="n">
+        <v>60777863478</v>
+      </c>
+      <c r="E8" s="20" t="n">
+        <v>45503369944</v>
+      </c>
+      <c r="F8" s="20" t="n">
         <v>42355371268</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="G8" s="20" t="n">
         <v>44508856492</v>
       </c>
-      <c r="F8" s="18" t="n">
+      <c r="H8" s="20" t="n">
         <v>39762517790</v>
       </c>
-      <c r="G8" s="18" t="n">
+      <c r="I8" s="20" t="n">
         <v>38125984102</v>
       </c>
-      <c r="H8" s="18" t="n">
+      <c r="J8" s="20" t="n">
         <v>24401706902</v>
       </c>
-      <c r="I8" s="18" t="n">
+      <c r="K8" s="20" t="n">
         <v>19398788428</v>
       </c>
-      <c r="J8" s="18" t="n">
-        <v>18672839545</v>
-      </c>
-      <c r="K8" s="18" t="n">
-        <v>35905561812</v>
-      </c>
-      <c r="L8" s="18" t="n">
+      <c r="L8" s="20" t="n">
+        <v>37345679090</v>
+      </c>
+      <c r="M8" s="20" t="n">
+        <v>17952780906</v>
+      </c>
+      <c r="N8" s="20" t="n">
         <v>17149123737</v>
       </c>
-      <c r="M8" s="18" t="n">
+      <c r="O8" s="20" t="n">
         <v>16095039591</v>
       </c>
-      <c r="N8" s="18" t="n">
+      <c r="P8" s="20" t="n">
         <v>11613965775</v>
       </c>
-      <c r="O8" s="18" t="n">
+      <c r="Q8" s="20" t="n">
         <v>5778000000</v>
       </c>
-      <c r="P8" s="18" t="n">
+      <c r="R8" s="20" t="n">
         <v>5304000000</v>
       </c>
-      <c r="Q8" s="18" t="n"/>
-      <c r="R8" s="18" t="n"/>
       <c r="S8" s="18" t="n"/>
       <c r="T8" s="5" t="n"/>
       <c r="U8" s="7" t="n"/>
@@ -958,47 +979,51 @@
       <c r="C9" s="18" t="n">
         <v>406380339115</v>
       </c>
-      <c r="D9" s="18" t="n">
+      <c r="D9" s="20" t="n">
+        <v>440787896768</v>
+      </c>
+      <c r="E9" s="20" t="n">
+        <v>406380339115</v>
+      </c>
+      <c r="F9" s="20" t="n">
         <v>386299285911</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="G9" s="20" t="n">
         <v>361666067730</v>
       </c>
-      <c r="F9" s="18" t="n">
+      <c r="H9" s="20" t="n">
         <v>349603540294</v>
       </c>
-      <c r="G9" s="18" t="n">
+      <c r="I9" s="20" t="n">
         <v>338223345881</v>
       </c>
-      <c r="H9" s="18" t="n">
+      <c r="J9" s="20" t="n">
         <v>320324031793</v>
       </c>
-      <c r="I9" s="18" t="n">
+      <c r="K9" s="20" t="n">
         <v>310122130019</v>
       </c>
-      <c r="J9" s="18" t="n">
+      <c r="L9" s="20" t="n">
         <v>301305356813</v>
       </c>
-      <c r="K9" s="18" t="n">
+      <c r="M9" s="20" t="n">
         <v>292173845314</v>
       </c>
-      <c r="L9" s="18" t="n">
+      <c r="N9" s="20" t="n">
         <v>282141339260</v>
       </c>
-      <c r="M9" s="18" t="n">
+      <c r="O9" s="20" t="n">
         <v>266561991235</v>
       </c>
-      <c r="N9" s="18" t="n">
+      <c r="P9" s="20" t="n">
         <v>260244201148</v>
       </c>
-      <c r="O9" s="18" t="n">
+      <c r="Q9" s="20" t="n">
         <v>255081056739</v>
       </c>
-      <c r="P9" s="18" t="n">
+      <c r="R9" s="20" t="n">
         <v>195976647933</v>
       </c>
-      <c r="Q9" s="18" t="n"/>
-      <c r="R9" s="18" t="n"/>
       <c r="S9" s="18" t="n"/>
       <c r="T9" s="5" t="n"/>
       <c r="U9" s="7" t="n"/>
@@ -1021,47 +1046,51 @@
       <c r="C10" s="18" t="n">
         <v>20081053204</v>
       </c>
-      <c r="D10" s="18" t="n">
+      <c r="D10" s="20" t="n">
+        <v>54488610857</v>
+      </c>
+      <c r="E10" s="20" t="n">
+        <v>20081053204</v>
+      </c>
+      <c r="F10" s="20" t="n">
         <v>69105125703</v>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="G10" s="20" t="n">
         <v>44789798437</v>
       </c>
-      <c r="F10" s="18" t="n">
+      <c r="H10" s="20" t="n">
         <v>29279508501</v>
       </c>
-      <c r="G10" s="18" t="n">
+      <c r="I10" s="20" t="n">
         <v>17899314088</v>
       </c>
-      <c r="H10" s="18" t="n">
+      <c r="J10" s="20" t="n">
         <v>39422804844</v>
       </c>
-      <c r="I10" s="18" t="n">
+      <c r="K10" s="20" t="n">
         <v>27980790759</v>
       </c>
-      <c r="J10" s="18" t="n">
+      <c r="L10" s="20" t="n">
         <v>19164017553</v>
       </c>
-      <c r="K10" s="18" t="n">
+      <c r="M10" s="20" t="n">
         <v>10032506054</v>
       </c>
-      <c r="L10" s="18" t="n">
+      <c r="N10" s="20" t="n">
         <v>33421456238</v>
       </c>
-      <c r="M10" s="18" t="n">
+      <c r="O10" s="20" t="n">
         <v>17536198779</v>
       </c>
-      <c r="N10" s="18" t="n">
+      <c r="P10" s="20" t="n">
         <v>11218408692</v>
       </c>
-      <c r="O10" s="18" t="n">
+      <c r="Q10" s="20" t="n">
         <v>6055264283</v>
       </c>
-      <c r="P10" s="18" t="n">
+      <c r="R10" s="20" t="n">
         <v>15834397481</v>
       </c>
-      <c r="Q10" s="18" t="n"/>
-      <c r="R10" s="18" t="n"/>
       <c r="S10" s="18" t="n"/>
       <c r="T10" s="5" t="n"/>
       <c r="U10" s="7" t="n"/>
@@ -1084,47 +1113,51 @@
       <c r="C11" s="18" t="n">
         <v>198217525096</v>
       </c>
-      <c r="D11" s="18" t="n">
+      <c r="D11" s="20" t="n">
+        <v>416305253678</v>
+      </c>
+      <c r="E11" s="20" t="n">
+        <v>198217525096</v>
+      </c>
+      <c r="F11" s="20" t="n">
         <v>656304660831</v>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="G11" s="20" t="n">
         <v>454671565688</v>
       </c>
-      <c r="F11" s="18" t="n">
+      <c r="H11" s="20" t="n">
         <v>276031872177</v>
       </c>
-      <c r="G11" s="18" t="n">
+      <c r="I11" s="20" t="n">
         <v>136421123584</v>
       </c>
-      <c r="H11" s="18" t="n">
+      <c r="J11" s="20" t="n">
         <v>428929469152</v>
       </c>
-      <c r="I11" s="18" t="n">
+      <c r="K11" s="20" t="n">
         <v>320168860120</v>
       </c>
-      <c r="J11" s="18" t="n">
+      <c r="L11" s="20" t="n">
         <v>211814927894</v>
       </c>
-      <c r="K11" s="18" t="n">
+      <c r="M11" s="20" t="n">
         <v>107283585181</v>
       </c>
-      <c r="L11" s="18" t="n">
+      <c r="N11" s="20" t="n">
         <v>344916761385</v>
       </c>
-      <c r="M11" s="18" t="n">
+      <c r="O11" s="20" t="n">
         <v>238738972578</v>
       </c>
-      <c r="N11" s="18" t="n">
+      <c r="P11" s="20" t="n">
         <v>148107135064</v>
       </c>
-      <c r="O11" s="18" t="n">
+      <c r="Q11" s="20" t="n">
         <v>69701660977</v>
       </c>
-      <c r="P11" s="18" t="n">
+      <c r="R11" s="20" t="n">
         <v>215876144768</v>
       </c>
-      <c r="Q11" s="18" t="n"/>
-      <c r="R11" s="18" t="n"/>
       <c r="S11" s="18" t="n"/>
       <c r="T11" s="5" t="n"/>
       <c r="U11" s="7" t="n"/>
@@ -1147,47 +1180,51 @@
       <c r="C12" s="18" t="n">
         <v>21593359177</v>
       </c>
-      <c r="D12" s="18" t="n">
+      <c r="D12" s="20" t="n">
+        <v>36280251489</v>
+      </c>
+      <c r="E12" s="20" t="n">
+        <v>21593359177</v>
+      </c>
+      <c r="F12" s="20" t="n">
         <v>92912280784</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="G12" s="20" t="n">
         <v>46744141072</v>
       </c>
-      <c r="F12" s="18" t="n">
+      <c r="H12" s="20" t="n">
         <v>19157874324</v>
       </c>
-      <c r="G12" s="18" t="n">
+      <c r="I12" s="20" t="n">
         <v>12746527545</v>
       </c>
-      <c r="H12" s="18" t="n">
+      <c r="J12" s="20" t="n">
         <v>33900503009</v>
       </c>
-      <c r="I12" s="18" t="n">
+      <c r="K12" s="20" t="n">
         <v>34013886562</v>
       </c>
-      <c r="J12" s="18" t="n">
+      <c r="L12" s="20" t="n">
         <v>17339806788</v>
       </c>
-      <c r="K12" s="18" t="n">
+      <c r="M12" s="20" t="n">
         <v>7054265677</v>
       </c>
-      <c r="L12" s="18" t="n">
+      <c r="N12" s="20" t="n">
         <v>59573516823</v>
       </c>
-      <c r="M12" s="18" t="n">
+      <c r="O12" s="20" t="n">
         <v>30910421282</v>
       </c>
-      <c r="N12" s="18" t="n">
+      <c r="P12" s="20" t="n">
         <v>5354597522</v>
       </c>
-      <c r="O12" s="18" t="n">
+      <c r="Q12" s="20" t="n">
         <v>10976626569</v>
       </c>
-      <c r="P12" s="18" t="n">
+      <c r="R12" s="20" t="n">
         <v>27606264949</v>
       </c>
-      <c r="Q12" s="18" t="n"/>
-      <c r="R12" s="18" t="n"/>
       <c r="S12" s="18" t="n"/>
       <c r="T12" s="5" t="n"/>
       <c r="U12" s="7" t="n"/>
@@ -1210,47 +1247,51 @@
       <c r="C13" s="18" t="n">
         <v>1894375000</v>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="D13" s="20" t="n">
         <v>1894375000</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="20" t="n">
         <v>1894375000</v>
       </c>
-      <c r="F13" s="18" t="n">
+      <c r="F13" s="20" t="n">
         <v>1894375000</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="G13" s="20" t="n">
         <v>1894375000</v>
       </c>
-      <c r="H13" s="18" t="n">
+      <c r="H13" s="20" t="n">
         <v>1894375000</v>
       </c>
-      <c r="I13" s="18" t="n">
+      <c r="I13" s="20" t="n">
         <v>1894375000</v>
       </c>
-      <c r="J13" s="18" t="n">
+      <c r="J13" s="20" t="n">
         <v>1894375000</v>
       </c>
-      <c r="K13" s="18" t="n">
+      <c r="K13" s="20" t="n">
         <v>1894375000</v>
       </c>
-      <c r="L13" s="18" t="n">
+      <c r="L13" s="20" t="n">
         <v>1894375000</v>
       </c>
-      <c r="M13" s="18" t="n">
+      <c r="M13" s="20" t="n">
         <v>1894375000</v>
       </c>
-      <c r="N13" s="18" t="n">
+      <c r="N13" s="20" t="n">
         <v>1894375000</v>
       </c>
-      <c r="O13" s="18" t="n">
+      <c r="O13" s="20" t="n">
         <v>1894375000</v>
       </c>
-      <c r="P13" s="18" t="n">
+      <c r="P13" s="20" t="n">
+        <v>1894375000</v>
+      </c>
+      <c r="Q13" s="20" t="n">
+        <v>1894375000</v>
+      </c>
+      <c r="R13" s="20" t="n">
         <v>1515500000</v>
       </c>
-      <c r="Q13" s="18" t="n"/>
-      <c r="R13" s="18" t="n"/>
       <c r="S13" s="18" t="n"/>
       <c r="T13" s="5" t="n"/>
       <c r="U13" s="7" t="n"/>
@@ -1268,13 +1309,13 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>196</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>332</v>
@@ -1289,13 +1330,13 @@
         <v>129</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>125</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="L14" s="5" t="n">
         <v>131</v>
@@ -2266,8 +2307,16 @@
       <c r="J25" s="17" t="n"/>
       <c r="K25" s="17" t="n"/>
       <c r="L25" s="17" t="n"/>
+      <c r="M25" s="17" t="n"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="17" t="n"/>
+      <c r="F26" s="17" t="n"/>
+      <c r="G26" s="17" t="n"/>
+      <c r="H26" s="17" t="n"/>
+      <c r="I26" s="17" t="n"/>
+      <c r="J26" s="17" t="n"/>
       <c r="K26" s="17" t="n"/>
       <c r="L26" s="17" t="n"/>
       <c r="M26" s="17" t="n"/>
@@ -2280,6 +2329,13 @@
       <c r="T26" s="19" t="n"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
+      <c r="D27" s="17" t="n"/>
+      <c r="E27" s="17" t="n"/>
+      <c r="F27" s="17" t="n"/>
+      <c r="G27" s="17" t="n"/>
+      <c r="H27" s="17" t="n"/>
+      <c r="I27" s="17" t="n"/>
+      <c r="J27" s="17" t="n"/>
       <c r="K27" s="17" t="n"/>
       <c r="L27" s="17" t="n"/>
       <c r="M27" s="17" t="n"/>
@@ -2292,6 +2348,13 @@
       <c r="T27" s="17" t="n"/>
     </row>
     <row r="28" ht="14.25" customHeight="1">
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="17" t="n"/>
+      <c r="G28" s="17" t="n"/>
+      <c r="H28" s="17" t="n"/>
+      <c r="I28" s="17" t="n"/>
+      <c r="J28" s="17" t="n"/>
       <c r="K28" s="17" t="n"/>
       <c r="L28" s="17" t="n"/>
       <c r="M28" s="17" t="n"/>
@@ -2304,6 +2367,13 @@
       <c r="T28" s="17" t="n"/>
     </row>
     <row r="29" ht="14.25" customHeight="1">
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="17" t="n"/>
+      <c r="G29" s="17" t="n"/>
+      <c r="H29" s="17" t="n"/>
+      <c r="I29" s="17" t="n"/>
+      <c r="J29" s="17" t="n"/>
       <c r="K29" s="17" t="n"/>
       <c r="L29" s="17" t="n"/>
       <c r="M29" s="17" t="n"/>
@@ -2315,26 +2385,285 @@
       <c r="S29" s="17" t="n"/>
       <c r="T29" s="17" t="n"/>
     </row>
-    <row r="30" ht="14.25" customHeight="1"/>
-    <row r="31" ht="14.25" customHeight="1"/>
-    <row r="32" ht="14.25" customHeight="1"/>
-    <row r="33" ht="14.25" customHeight="1"/>
-    <row r="34" ht="14.25" customHeight="1"/>
-    <row r="35" ht="14.25" customHeight="1"/>
-    <row r="36" ht="14.25" customHeight="1"/>
-    <row r="37" ht="14.25" customHeight="1"/>
-    <row r="38" ht="14.25" customHeight="1"/>
+    <row r="30" ht="14.25" customHeight="1">
+      <c r="D30" s="17" t="n"/>
+      <c r="E30" s="17" t="n"/>
+      <c r="F30" s="17" t="n"/>
+      <c r="G30" s="17" t="n"/>
+      <c r="H30" s="17" t="n"/>
+      <c r="I30" s="17" t="n"/>
+      <c r="J30" s="17" t="n"/>
+      <c r="K30" s="17" t="n"/>
+      <c r="L30" s="17" t="n"/>
+      <c r="M30" s="17" t="n"/>
+    </row>
+    <row r="31" ht="14.25" customHeight="1">
+      <c r="D31" s="17" t="n"/>
+      <c r="E31" s="17" t="n"/>
+      <c r="F31" s="17" t="n"/>
+      <c r="G31" s="17" t="n"/>
+      <c r="H31" s="17" t="n"/>
+      <c r="I31" s="17" t="n"/>
+      <c r="J31" s="17" t="n"/>
+      <c r="K31" s="17" t="n"/>
+      <c r="L31" s="17" t="n"/>
+      <c r="M31" s="17" t="n"/>
+    </row>
+    <row r="32" ht="14.25" customHeight="1">
+      <c r="D32" s="17" t="n"/>
+      <c r="E32" s="17" t="n"/>
+      <c r="F32" s="17" t="n"/>
+      <c r="G32" s="17" t="n"/>
+      <c r="H32" s="17" t="n"/>
+      <c r="I32" s="17" t="n"/>
+      <c r="J32" s="17" t="n"/>
+      <c r="K32" s="17" t="n"/>
+      <c r="L32" s="17" t="n"/>
+      <c r="M32" s="17" t="n"/>
+    </row>
+    <row r="33" ht="14.25" customHeight="1">
+      <c r="D33" s="17" t="n"/>
+      <c r="E33" s="17" t="n"/>
+      <c r="F33" s="17" t="n"/>
+      <c r="G33" s="17" t="n"/>
+      <c r="H33" s="17" t="n"/>
+      <c r="I33" s="17" t="n"/>
+      <c r="J33" s="17" t="n"/>
+      <c r="K33" s="17" t="n"/>
+      <c r="L33" s="17" t="n"/>
+      <c r="M33" s="17" t="n"/>
+    </row>
+    <row r="34" ht="14.25" customHeight="1">
+      <c r="D34" s="17" t="n"/>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="17" t="n"/>
+      <c r="G34" s="17" t="n"/>
+      <c r="H34" s="17" t="n"/>
+      <c r="I34" s="17" t="n"/>
+      <c r="J34" s="17" t="n"/>
+      <c r="K34" s="17" t="n"/>
+      <c r="L34" s="17" t="n"/>
+      <c r="M34" s="17" t="n"/>
+    </row>
+    <row r="35" ht="14.25" customHeight="1">
+      <c r="D35" s="17" t="n"/>
+      <c r="E35" s="17" t="n"/>
+      <c r="F35" s="17" t="n"/>
+      <c r="G35" s="17" t="n"/>
+      <c r="H35" s="17" t="n"/>
+      <c r="I35" s="17" t="n"/>
+      <c r="J35" s="17" t="n"/>
+      <c r="K35" s="17" t="n"/>
+      <c r="L35" s="17" t="n"/>
+      <c r="M35" s="17" t="n"/>
+    </row>
+    <row r="36" ht="14.25" customHeight="1">
+      <c r="D36" s="17" t="n"/>
+      <c r="E36" s="17" t="n"/>
+      <c r="F36" s="17" t="n"/>
+      <c r="G36" s="17" t="n"/>
+      <c r="H36" s="17" t="n"/>
+      <c r="I36" s="17" t="n"/>
+      <c r="J36" s="17" t="n"/>
+      <c r="K36" s="17" t="n"/>
+      <c r="L36" s="17" t="n"/>
+      <c r="M36" s="17" t="n"/>
+    </row>
+    <row r="37" ht="14.25" customHeight="1">
+      <c r="D37" s="17" t="n"/>
+      <c r="E37" s="17" t="n"/>
+      <c r="F37" s="17" t="n"/>
+      <c r="G37" s="17" t="n"/>
+      <c r="H37" s="17" t="n"/>
+      <c r="I37" s="17" t="n"/>
+      <c r="J37" s="17" t="n"/>
+      <c r="K37" s="17" t="n"/>
+      <c r="L37" s="17" t="n"/>
+      <c r="M37" s="17" t="n"/>
+    </row>
+    <row r="38" ht="14.25" customHeight="1">
+      <c r="D38" s="17" t="n"/>
+      <c r="E38" s="17" t="n"/>
+      <c r="F38" s="17" t="n"/>
+      <c r="G38" s="17" t="n"/>
+      <c r="H38" s="17" t="n"/>
+      <c r="I38" s="17" t="n"/>
+      <c r="J38" s="17" t="n"/>
+      <c r="K38" s="17" t="n"/>
+      <c r="L38" s="17" t="n"/>
+      <c r="M38" s="17" t="n"/>
+    </row>
     <row r="39" ht="14.25" customHeight="1"/>
-    <row r="40" ht="14.25" customHeight="1"/>
-    <row r="41" ht="14.25" customHeight="1"/>
-    <row r="42" ht="14.25" customHeight="1"/>
-    <row r="43" ht="14.25" customHeight="1"/>
-    <row r="44" ht="14.25" customHeight="1"/>
-    <row r="45" ht="14.25" customHeight="1"/>
-    <row r="46" ht="14.25" customHeight="1"/>
-    <row r="47" ht="14.25" customHeight="1"/>
-    <row r="48" ht="14.25" customHeight="1"/>
-    <row r="49" ht="14.25" customHeight="1"/>
+    <row r="40" ht="14.25" customHeight="1">
+      <c r="D40" s="17" t="n"/>
+      <c r="E40" s="17" t="n"/>
+      <c r="F40" s="17" t="n"/>
+      <c r="G40" s="17" t="n"/>
+      <c r="H40" s="17" t="n"/>
+      <c r="I40" s="17" t="n"/>
+      <c r="J40" s="17" t="n"/>
+      <c r="K40" s="17" t="n"/>
+      <c r="L40" s="17" t="n"/>
+      <c r="M40" s="17" t="n"/>
+      <c r="N40" s="17" t="n"/>
+      <c r="O40" s="17" t="n"/>
+      <c r="P40" s="17" t="n"/>
+      <c r="Q40" s="17" t="n"/>
+      <c r="R40" s="17" t="n"/>
+    </row>
+    <row r="41" ht="14.25" customHeight="1">
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="17" t="n"/>
+      <c r="F41" s="17" t="n"/>
+      <c r="G41" s="17" t="n"/>
+      <c r="H41" s="17" t="n"/>
+      <c r="I41" s="17" t="n"/>
+      <c r="J41" s="17" t="n"/>
+      <c r="K41" s="17" t="n"/>
+      <c r="L41" s="17" t="n"/>
+      <c r="M41" s="17" t="n"/>
+      <c r="N41" s="17" t="n"/>
+      <c r="O41" s="17" t="n"/>
+      <c r="P41" s="17" t="n"/>
+      <c r="Q41" s="17" t="n"/>
+      <c r="R41" s="17" t="n"/>
+    </row>
+    <row r="42" ht="14.25" customHeight="1">
+      <c r="D42" s="17" t="n"/>
+      <c r="E42" s="17" t="n"/>
+      <c r="F42" s="17" t="n"/>
+      <c r="G42" s="17" t="n"/>
+      <c r="H42" s="17" t="n"/>
+      <c r="I42" s="17" t="n"/>
+      <c r="J42" s="17" t="n"/>
+      <c r="K42" s="17" t="n"/>
+      <c r="L42" s="17" t="n"/>
+      <c r="M42" s="17" t="n"/>
+      <c r="N42" s="17" t="n"/>
+      <c r="O42" s="17" t="n"/>
+      <c r="P42" s="17" t="n"/>
+      <c r="Q42" s="17" t="n"/>
+      <c r="R42" s="17" t="n"/>
+    </row>
+    <row r="43" ht="14.25" customHeight="1">
+      <c r="D43" s="17" t="n"/>
+      <c r="E43" s="17" t="n"/>
+      <c r="F43" s="17" t="n"/>
+      <c r="G43" s="17" t="n"/>
+      <c r="H43" s="17" t="n"/>
+      <c r="I43" s="17" t="n"/>
+      <c r="J43" s="17" t="n"/>
+      <c r="K43" s="17" t="n"/>
+      <c r="L43" s="17" t="n"/>
+      <c r="M43" s="17" t="n"/>
+      <c r="N43" s="17" t="n"/>
+      <c r="O43" s="17" t="n"/>
+      <c r="P43" s="17" t="n"/>
+      <c r="Q43" s="17" t="n"/>
+      <c r="R43" s="17" t="n"/>
+    </row>
+    <row r="44" ht="14.25" customHeight="1">
+      <c r="D44" s="17" t="n"/>
+      <c r="E44" s="17" t="n"/>
+      <c r="F44" s="17" t="n"/>
+      <c r="G44" s="17" t="n"/>
+      <c r="H44" s="17" t="n"/>
+      <c r="I44" s="17" t="n"/>
+      <c r="J44" s="17" t="n"/>
+      <c r="K44" s="17" t="n"/>
+      <c r="L44" s="17" t="n"/>
+      <c r="M44" s="17" t="n"/>
+      <c r="N44" s="17" t="n"/>
+      <c r="O44" s="17" t="n"/>
+      <c r="P44" s="17" t="n"/>
+      <c r="Q44" s="17" t="n"/>
+      <c r="R44" s="17" t="n"/>
+    </row>
+    <row r="45" ht="14.25" customHeight="1">
+      <c r="D45" s="17" t="n"/>
+      <c r="E45" s="17" t="n"/>
+      <c r="F45" s="17" t="n"/>
+      <c r="G45" s="17" t="n"/>
+      <c r="H45" s="17" t="n"/>
+      <c r="I45" s="17" t="n"/>
+      <c r="J45" s="17" t="n"/>
+      <c r="K45" s="17" t="n"/>
+      <c r="L45" s="17" t="n"/>
+      <c r="M45" s="17" t="n"/>
+      <c r="N45" s="17" t="n"/>
+      <c r="O45" s="17" t="n"/>
+      <c r="P45" s="17" t="n"/>
+      <c r="Q45" s="17" t="n"/>
+      <c r="R45" s="17" t="n"/>
+    </row>
+    <row r="46" ht="14.25" customHeight="1">
+      <c r="D46" s="17" t="n"/>
+      <c r="E46" s="17" t="n"/>
+      <c r="F46" s="17" t="n"/>
+      <c r="G46" s="17" t="n"/>
+      <c r="H46" s="17" t="n"/>
+      <c r="I46" s="17" t="n"/>
+      <c r="J46" s="17" t="n"/>
+      <c r="K46" s="17" t="n"/>
+      <c r="L46" s="17" t="n"/>
+      <c r="M46" s="17" t="n"/>
+      <c r="N46" s="17" t="n"/>
+      <c r="O46" s="17" t="n"/>
+      <c r="P46" s="17" t="n"/>
+      <c r="Q46" s="17" t="n"/>
+      <c r="R46" s="17" t="n"/>
+    </row>
+    <row r="47" ht="14.25" customHeight="1">
+      <c r="D47" s="17" t="n"/>
+      <c r="E47" s="17" t="n"/>
+      <c r="F47" s="17" t="n"/>
+      <c r="G47" s="17" t="n"/>
+      <c r="H47" s="17" t="n"/>
+      <c r="I47" s="17" t="n"/>
+      <c r="J47" s="17" t="n"/>
+      <c r="K47" s="17" t="n"/>
+      <c r="L47" s="17" t="n"/>
+      <c r="M47" s="17" t="n"/>
+      <c r="N47" s="17" t="n"/>
+      <c r="O47" s="17" t="n"/>
+      <c r="P47" s="17" t="n"/>
+      <c r="Q47" s="17" t="n"/>
+      <c r="R47" s="17" t="n"/>
+    </row>
+    <row r="48" ht="14.25" customHeight="1">
+      <c r="D48" s="17" t="n"/>
+      <c r="E48" s="17" t="n"/>
+      <c r="F48" s="17" t="n"/>
+      <c r="G48" s="17" t="n"/>
+      <c r="H48" s="17" t="n"/>
+      <c r="I48" s="17" t="n"/>
+      <c r="J48" s="17" t="n"/>
+      <c r="K48" s="17" t="n"/>
+      <c r="L48" s="17" t="n"/>
+      <c r="M48" s="17" t="n"/>
+      <c r="N48" s="17" t="n"/>
+      <c r="O48" s="17" t="n"/>
+      <c r="P48" s="17" t="n"/>
+      <c r="Q48" s="17" t="n"/>
+      <c r="R48" s="17" t="n"/>
+    </row>
+    <row r="49" ht="14.25" customHeight="1">
+      <c r="D49" s="17" t="n"/>
+      <c r="E49" s="17" t="n"/>
+      <c r="F49" s="17" t="n"/>
+      <c r="G49" s="17" t="n"/>
+      <c r="H49" s="17" t="n"/>
+      <c r="I49" s="17" t="n"/>
+      <c r="J49" s="17" t="n"/>
+      <c r="K49" s="17" t="n"/>
+      <c r="L49" s="17" t="n"/>
+      <c r="M49" s="17" t="n"/>
+      <c r="N49" s="17" t="n"/>
+      <c r="O49" s="17" t="n"/>
+      <c r="P49" s="17" t="n"/>
+      <c r="Q49" s="17" t="n"/>
+      <c r="R49" s="17" t="n"/>
+    </row>
     <row r="50" ht="14.25" customHeight="1"/>
     <row r="51" ht="14.25" customHeight="1"/>
     <row r="52" ht="14.25" customHeight="1"/>
